--- a/Penerima Manfaat - Busui.xlsx
+++ b/Penerima Manfaat - Busui.xlsx
@@ -1193,7 +1193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1000"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1251,7 +1251,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>66</v>
       </c>
@@ -1320,7 +1320,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>70</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>74</v>
       </c>
@@ -1366,7 +1366,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>78</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>82</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>86</v>
       </c>
@@ -1435,7 +1435,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>90</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>94</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>98</v>
       </c>
@@ -1504,7 +1504,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>102</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>106</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>110</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>114</v>
       </c>
@@ -1596,7 +1596,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>118</v>
       </c>
@@ -1619,7 +1619,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>122</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>126</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>130</v>
       </c>
@@ -1688,7 +1688,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>134</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>138</v>
       </c>
@@ -1734,7 +1734,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>142</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>146</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>150</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>153</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>157</v>
       </c>
@@ -1849,7 +1849,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>161</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>165</v>
       </c>
@@ -1895,7 +1895,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>169</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>173</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>177</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>180</v>
       </c>
@@ -1987,7 +1987,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>184</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>188</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>191</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>195</v>
       </c>
@@ -2079,7 +2079,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>199</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>203</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>207</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>211</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>215</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>219</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>223</v>
       </c>
@@ -2240,7 +2240,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>227</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>231</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>235</v>
       </c>
@@ -2309,7 +2309,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>239</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>243</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>247</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>251</v>
       </c>
@@ -2401,7 +2401,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>255</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>259</v>
       </c>
@@ -2447,7 +2447,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>263</v>
       </c>
@@ -2470,7 +2470,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>267</v>
       </c>
@@ -2493,7 +2493,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>271</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>275</v>
       </c>
